--- a/data_dashboard_tw2.xlsx
+++ b/data_dashboard_tw2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2853B574-E01E-4436-9C3B-4BD880303016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763D6C7E-04EF-4387-AE91-EBABBC7D9E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Proporsi kabupaten/kota yang melakukan pemeriksaan kesehatan gratis pada &gt;80% populasi target</t>
   </si>
@@ -123,9 +123,6 @@
   </si>
   <si>
     <t>84 Kab/Kota</t>
-  </si>
-  <si>
-    <t>6 Kab/Kota</t>
   </si>
 </sst>
 </file>
@@ -637,8 +634,8 @@
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="17"/>
-      <c r="H5" s="27" t="s">
-        <v>29</v>
+      <c r="H5" s="27">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -680,7 +677,7 @@
       <c r="F7" s="14"/>
       <c r="G7" s="14"/>
       <c r="H7" s="10">
-        <f t="shared" ref="H3:H10" si="0">C7-D7</f>
+        <f t="shared" ref="H7:H10" si="0">C7-D7</f>
         <v>0.2</v>
       </c>
     </row>
